--- a/Data/X_Guangdong_Demand_and_Policy.xlsx
+++ b/Data/X_Guangdong_Demand_and_Policy.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\statistical-model\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D644B8F8-AA70-421B-BF13-7A7F93602491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DECE15-9EDF-405C-832A-23EBB8FEEAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="23">
   <si>
     <t>province_code</t>
   </si>
@@ -108,6 +117,10 @@
   </si>
   <si>
     <t>NaN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -436,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
@@ -446,8 +459,8 @@
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="11.88671875" customWidth="1"/>
     <col min="7" max="7" width="19.109375" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
-    <col min="9" max="9" width="17.21875" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -473,10 +486,10 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -725,7 +738,7 @@
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="I12" t="s">
+      <c r="H12" t="s">
         <v>12</v>
       </c>
     </row>
@@ -975,7 +988,7 @@
       <c r="F23">
         <v>1</v>
       </c>
-      <c r="I23" t="s">
+      <c r="H23" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1225,7 +1238,257 @@
       <c r="F34">
         <v>1</v>
       </c>
-      <c r="I34" t="s">
+      <c r="H34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35">
+        <v>2015</v>
+      </c>
+      <c r="D35">
+        <v>537.79999999999995</v>
+      </c>
+      <c r="E35" s="1">
+        <v>71.936499999999995</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36">
+        <v>2016</v>
+      </c>
+      <c r="D36">
+        <v>558.44000000000005</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37">
+        <v>2017</v>
+      </c>
+      <c r="D37">
+        <v>538.4</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38">
+        <v>2018</v>
+      </c>
+      <c r="D38">
+        <v>503.57</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39">
+        <v>2019</v>
+      </c>
+      <c r="D39">
+        <v>470.49</v>
+      </c>
+      <c r="E39" s="1">
+        <v>111.7715</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40">
+        <v>2020</v>
+      </c>
+      <c r="D40">
+        <v>528.32000000000005</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41">
+        <v>2021</v>
+      </c>
+      <c r="D41">
+        <v>510.11</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42">
+        <v>2022</v>
+      </c>
+      <c r="D42">
+        <v>553.07000000000005</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43">
+        <v>2023</v>
+      </c>
+      <c r="D43">
+        <v>555.73</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44">
+        <v>2024</v>
+      </c>
+      <c r="D44">
+        <v>545.73</v>
+      </c>
+      <c r="E44" s="1">
+        <v>103.7259</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45">
+        <v>2025</v>
+      </c>
+      <c r="D45">
+        <v>495.14</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
         <v>12</v>
       </c>
     </row>
